--- a/ident_template.xlsx
+++ b/ident_template.xlsx
@@ -969,7 +969,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="482">
+  <cellXfs count="483">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2295,6 +2295,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2705,7 +2708,6 @@
     <col width="9.140625" customWidth="1" min="71" max="73"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="34.5" customHeight="1">
       <c r="A2" s="333" t="inlineStr">
         <is>
@@ -3435,14 +3437,14 @@
       <c r="AH7" s="12" t="n"/>
       <c r="AI7" s="174" t="n"/>
       <c r="AJ7" s="165" t="n"/>
-      <c r="AK7" s="144" t="n"/>
+      <c r="AK7" s="482" t="n"/>
       <c r="AL7" s="35" t="n"/>
       <c r="AM7" s="150">
         <f>AK7+AL7</f>
         <v/>
       </c>
-      <c r="AN7" s="150" t="n"/>
-      <c r="AO7" s="150" t="n"/>
+      <c r="AN7" s="35" t="n"/>
+      <c r="AO7" s="35" t="n"/>
       <c r="AP7" s="11" t="n"/>
       <c r="AQ7" s="35" t="n"/>
       <c r="AR7" s="12" t="n"/>
